--- a/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643696557</v>
+        <v>10.8449764321942</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907230691024</v>
+        <v>37.78907229028454</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.147884050442774</v>
+        <v>5.122759520759856</v>
       </c>
       <c r="C2" t="n">
-        <v>7.298312433370788</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="D2" t="n">
-        <v>34.95512700970768</v>
+        <v>32.81982575297087</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.4057649014902</v>
+        <v>14.05862712481433</v>
       </c>
       <c r="C3" t="n">
-        <v>40.69835107955153</v>
+        <v>28.08780181850124</v>
       </c>
       <c r="D3" t="n">
-        <v>86.65886985386595</v>
+        <v>90.76257525761763</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.5629677073567</v>
+        <v>31.35800342134737</v>
       </c>
       <c r="C4" t="n">
-        <v>92.23617856169209</v>
+        <v>77.38037230102935</v>
       </c>
       <c r="D4" t="n">
-        <v>108.8021893231528</v>
+        <v>96.56274069430778</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.96280106489242</v>
+        <v>38.31270415823178</v>
       </c>
       <c r="C5" t="n">
-        <v>128.6334929489384</v>
+        <v>130.4006388165826</v>
       </c>
       <c r="D5" t="n">
-        <v>83.57127332400975</v>
+        <v>62.39006660488482</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.4428346345401</v>
+        <v>34.49566908412018</v>
       </c>
       <c r="C6" t="n">
-        <v>122.4052855131966</v>
+        <v>157.7462393706733</v>
       </c>
       <c r="D6" t="n">
-        <v>53.49445065670446</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="C7" t="n">
-        <v>82.04465564390594</v>
+        <v>141.0928530635346</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>46.81463927700915</v>
+        <v>90.54168202416209</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695430132845261</v>
+        <v>7.661517634975018</v>
       </c>
       <c r="C21" t="n">
-        <v>94.26901912735444</v>
+        <v>92.89590132407209</v>
       </c>
       <c r="D21" t="n">
-        <v>8.657358899450919</v>
+        <v>7.661517634975018</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.745768402329081</v>
+        <v>6.530585728649783</v>
       </c>
       <c r="C2" t="n">
-        <v>13.63843910739669</v>
+        <v>13.98205080388307</v>
       </c>
       <c r="D2" t="n">
-        <v>26.82036553231861</v>
+        <v>39.63119132503524</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.53830084156352</v>
+        <v>15.37907778702628</v>
       </c>
       <c r="C3" t="n">
-        <v>34.51824928131785</v>
+        <v>30.34582153826891</v>
       </c>
       <c r="D3" t="n">
-        <v>92.81442795949346</v>
+        <v>94.19378348396022</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.77618688562751</v>
+        <v>28.75440850968483</v>
       </c>
       <c r="C4" t="n">
-        <v>95.80974020515048</v>
+        <v>73.75575977695013</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5003351140593</v>
+        <v>114.1114809077195</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.5398887885403</v>
+        <v>42.3378697456437</v>
       </c>
       <c r="C5" t="n">
-        <v>147.1639808665969</v>
+        <v>134.5485228670254</v>
       </c>
       <c r="D5" t="n">
-        <v>99.52467351802042</v>
+        <v>79.42338927356697</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.69442408873454</v>
+        <v>41.861722109084</v>
       </c>
       <c r="C6" t="n">
-        <v>161.1273784640993</v>
+        <v>180.4884249395506</v>
       </c>
       <c r="D6" t="n">
-        <v>65.61019907481435</v>
+        <v>51.84413276586557</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.58398531977338</v>
+        <v>31.62013005838127</v>
       </c>
       <c r="C7" t="n">
-        <v>125.282788034344</v>
+        <v>179.0609637775758</v>
       </c>
       <c r="D7" t="n">
-        <v>45.99291644855457</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.52419652080556</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="C8" t="n">
-        <v>75.8547363686298</v>
+        <v>133.2673421129833</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>77.21249344360311</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.874148486784597</v>
+        <v>7.83244891734561</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3639303281998</v>
+        <v>100.8427798108247</v>
       </c>
       <c r="D21" t="n">
-        <v>9.842685608480748</v>
+        <v>8.811505032013811</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.193445355465627</v>
+        <v>6.394122797759476</v>
       </c>
       <c r="C2" t="n">
-        <v>9.447358157967058</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D2" t="n">
-        <v>26.58180084018664</v>
+        <v>35.42145716922492</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.47586989911922</v>
+        <v>17.78926840095221</v>
       </c>
       <c r="C3" t="n">
-        <v>42.77474747403353</v>
+        <v>40.65417243286042</v>
       </c>
       <c r="D3" t="n">
-        <v>91.82777151672542</v>
+        <v>100.6389571623405</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.69135567243478</v>
+        <v>28.18008610270045</v>
       </c>
       <c r="C4" t="n">
-        <v>90.27071965778997</v>
+        <v>73.62813257539804</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3313766979376</v>
+        <v>129.4650332544354</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.5398887885403</v>
+        <v>42.28878236043136</v>
       </c>
       <c r="C5" t="n">
-        <v>159.7548951735622</v>
+        <v>134.6712413300562</v>
       </c>
       <c r="D5" t="n">
-        <v>116.6316272645211</v>
+        <v>95.05772146369743</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.76613272887356</v>
+        <v>48.10072876957248</v>
       </c>
       <c r="C6" t="n">
-        <v>190.4708355963322</v>
+        <v>192.6041733576605</v>
       </c>
       <c r="D6" t="n">
-        <v>77.20267596656069</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.30935800449154</v>
+        <v>38.5669768136317</v>
       </c>
       <c r="C7" t="n">
-        <v>169.9581990637993</v>
+        <v>211.3997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>52.58044354405067</v>
+        <v>45.63359678880023</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.699389580518</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="C8" t="n">
-        <v>114.491417269263</v>
+        <v>175.1585166531947</v>
       </c>
       <c r="D8" t="n">
-        <v>41.55738032076748</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>113.3781153726471</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>61.78138302825178</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.0362345289958</v>
+        <v>7.986210175676614</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4982247736923</v>
+        <v>107.8138373716343</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04982247736922</v>
+        <v>9.982762719595769</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80172802147115</v>
+        <v>5.969026041820607</v>
       </c>
       <c r="C2" t="n">
-        <v>6.499169802113885</v>
+        <v>8.438121518001335</v>
       </c>
       <c r="D2" t="n">
-        <v>22.14626471239955</v>
+        <v>29.30320547635879</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>20.14546289114455</v>
       </c>
       <c r="C3" t="n">
-        <v>60.68182559949535</v>
+        <v>57.01008918561228</v>
       </c>
       <c r="D3" t="n">
-        <v>99.85355899894309</v>
+        <v>107.0792221021996</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.9909275909503</v>
+        <v>20.31825048709199</v>
       </c>
       <c r="C4" t="n">
-        <v>129.1332025304</v>
+        <v>106.0964926502486</v>
       </c>
       <c r="D4" t="n">
-        <v>130.907220631974</v>
+        <v>118.6805347232842</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.77087723647878</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="C5" t="n">
-        <v>113.8091026148115</v>
+        <v>115.0853746303324</v>
       </c>
       <c r="D5" t="n">
-        <v>77.45989386507335</v>
+        <v>62.41461029749098</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.14470212761856</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9398549859256</v>
+        <v>139.2304776685784</v>
       </c>
       <c r="D6" t="n">
-        <v>34.61642405174254</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>80.4876037849705</v>
+        <v>123.186756685777</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14843349645307</v>
+        <v>83.53200341583985</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.944261365036184</v>
+        <v>3.526437753654543</v>
       </c>
       <c r="C2" t="n">
-        <v>3.503857556456866</v>
+        <v>3.865140711619692</v>
       </c>
       <c r="D2" t="n">
-        <v>15.25537757629119</v>
+        <v>20.2514916432032</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>20.97994843975434</v>
       </c>
       <c r="C3" t="n">
-        <v>43.55032816038851</v>
+        <v>46.08814597586652</v>
       </c>
       <c r="D3" t="n">
-        <v>96.53525175858886</v>
+        <v>106.1269268290802</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.34676222824415</v>
+        <v>27.60576369571606</v>
       </c>
       <c r="C4" t="n">
-        <v>144.6016193585127</v>
+        <v>125.5468781667864</v>
       </c>
       <c r="D4" t="n">
-        <v>146.7074681841221</v>
+        <v>140.3516335468283</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>29.67332436085985</v>
       </c>
       <c r="C5" t="n">
-        <v>170.0387023755476</v>
+        <v>153.2017292477148</v>
       </c>
       <c r="D5" t="n">
-        <v>98.32203258031808</v>
+        <v>80.79783605951251</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.6126359296458</v>
+        <v>28.33716573537994</v>
       </c>
       <c r="C6" t="n">
-        <v>144.5839478998363</v>
+        <v>162.5361864196935</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07556318216056</v>
+        <v>36.79001346894498</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>110.3111355445801</v>
+        <v>155.3458662337898</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>64.17193868809275</v>
+        <v>108.5665698741335</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -2125,7 +2125,7 @@
         <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>51.25312064790897</v>
       </c>
       <c r="D9" t="n">
         <v>28.51093507903161</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.31989518733098</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.442989198793564</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C2" t="n">
-        <v>6.803511590430396</v>
+        <v>13.90252923983908</v>
       </c>
       <c r="D2" t="n">
-        <v>15.53812091511427</v>
+        <v>16.76923253623977</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76410281354028</v>
+        <v>16.50808764691012</v>
       </c>
       <c r="C3" t="n">
-        <v>28.04853191033137</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D3" t="n">
-        <v>87.29209712310515</v>
+        <v>99.34795893125597</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.31596819651401</v>
+        <v>33.40003864618074</v>
       </c>
       <c r="C4" t="n">
-        <v>126.5296076187374</v>
+        <v>120.2375865822196</v>
       </c>
       <c r="D4" t="n">
-        <v>159.2659848168473</v>
+        <v>155.5520332516816</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.88854809226815</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>216.2790192455724</v>
+        <v>191.293540172491</v>
       </c>
       <c r="D5" t="n">
-        <v>123.5529485794611</v>
+        <v>107.3786551519949</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.4428346345401</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="C6" t="n">
-        <v>203.8746370024139</v>
+        <v>198.4809151152819</v>
       </c>
       <c r="D6" t="n">
-        <v>60.33723215530473</v>
+        <v>50.07305990740432</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="C7" t="n">
-        <v>154.3876804744449</v>
+        <v>192.3557911884861</v>
       </c>
       <c r="D7" t="n">
-        <v>36.59071868498287</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>100.7224057172015</v>
+        <v>150.7915386337888</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>84.53436782187582</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>35.58835427894688</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
         <v>29.852984190737</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.041053477129119</v>
+        <v>2.0930861054542</v>
       </c>
       <c r="C2" t="n">
-        <v>3.245657910239955</v>
+        <v>6.698464586075987</v>
       </c>
       <c r="D2" t="n">
-        <v>10.83653115947629</v>
+        <v>11.70439613003047</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05862712481433</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="C3" t="n">
-        <v>29.19717672430014</v>
+        <v>42.01389300324225</v>
       </c>
       <c r="D3" t="n">
-        <v>84.33703653332225</v>
+        <v>95.50932540765095</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.25139383221197</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>119.0506536077852</v>
+        <v>117.6850425511779</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5317196495287</v>
+        <v>169.7314153441183</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.41025703385071</v>
+        <v>35.9810533606456</v>
       </c>
       <c r="C5" t="n">
-        <v>253.6099756995573</v>
+        <v>229.778050178966</v>
       </c>
       <c r="D5" t="n">
-        <v>130.2042892757333</v>
+        <v>110.3484419573415</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.48558956517046</v>
+        <v>26.76735115628929</v>
       </c>
       <c r="C6" t="n">
-        <v>238.3703060865341</v>
+        <v>232.2923060495421</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>48.70450360768427</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.94684675525043</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>150.9142570968197</v>
+        <v>197.8054726947601</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>70.01333752836128</v>
+        <v>105.1451791248334</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>27.17968519207294</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
         <v>23.34596040698915</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.916371518689774</v>
+        <v>2.750857067299563</v>
       </c>
       <c r="C2" t="n">
-        <v>5.320090809313465</v>
+        <v>7.799985510240909</v>
       </c>
       <c r="D2" t="n">
-        <v>12.38278379366502</v>
+        <v>16.30192062901829</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.69123249924777</v>
+        <v>11.91841712955628</v>
       </c>
       <c r="C3" t="n">
-        <v>20.93576979306323</v>
+        <v>34.23354244708628</v>
       </c>
       <c r="D3" t="n">
-        <v>74.94171100368027</v>
+        <v>84.50884238156544</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.68608708101505</v>
+        <v>33.74463209037137</v>
       </c>
       <c r="C4" t="n">
-        <v>97.83901270982864</v>
+        <v>112.5544290487841</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1991281619673</v>
+        <v>176.6360469480861</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.42346172236243</v>
+        <v>43.58959806855839</v>
       </c>
       <c r="C5" t="n">
-        <v>240.1109447661637</v>
+        <v>225.7283408989479</v>
       </c>
       <c r="D5" t="n">
-        <v>154.1589332593554</v>
+        <v>139.1627370769854</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>34.89818564286137</v>
       </c>
       <c r="C6" t="n">
-        <v>310.1792601659628</v>
+        <v>289.4496573907914</v>
       </c>
       <c r="D6" t="n">
-        <v>79.25551041614078</v>
+        <v>64.56365602208724</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>230.14424207265</v>
+        <v>254.6977521558627</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>120.8335074386974</v>
+        <v>165.5619328441821</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>48.59062087399162</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.266454538478385</v>
+        <v>1.821141991377833</v>
       </c>
       <c r="C2" t="n">
-        <v>3.68744437715102</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="D2" t="n">
-        <v>9.904852588146069</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.071348787240529</v>
+        <v>10.9415781638307</v>
       </c>
       <c r="C3" t="n">
-        <v>21.00449213236051</v>
+        <v>33.14871123389355</v>
       </c>
       <c r="D3" t="n">
-        <v>69.52246367623788</v>
+        <v>79.70809610779854</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.84000048640355</v>
+        <v>30.38803668955152</v>
       </c>
       <c r="C4" t="n">
-        <v>81.52825635147212</v>
+        <v>103.5567113393621</v>
       </c>
       <c r="D4" t="n">
-        <v>170.5865175945173</v>
+        <v>178.3334887287288</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C5" t="n">
-        <v>226.3664769067084</v>
+        <v>226.5628264475577</v>
       </c>
       <c r="D5" t="n">
-        <v>170.8977316167635</v>
+        <v>158.7731474693154</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>347.4522935053972</v>
+        <v>324.3075913777787</v>
       </c>
       <c r="D6" t="n">
-        <v>93.18258334858602</v>
+        <v>77.60519252530189</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>295.7200799778157</v>
+        <v>309.9730931480709</v>
       </c>
       <c r="D7" t="n">
-        <v>47.01098881785852</v>
+        <v>42.75903951076558</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>164.1433074115454</v>
+        <v>207.6200044941154</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>54.47030787472577</v>
+        <v>70.77811898996953</v>
       </c>
       <c r="D9" t="n">
         <v>31.94999728700819</v>
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>10.75504610002381</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.827032477603314</v>
+        <v>2.677225989481052</v>
       </c>
       <c r="C2" t="n">
-        <v>10.24355554611122</v>
+        <v>15.33489914033518</v>
       </c>
       <c r="D2" t="n">
-        <v>12.94139823738145</v>
+        <v>20.29174329907732</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.872233929727672</v>
+        <v>8.717919613711677</v>
       </c>
       <c r="C3" t="n">
-        <v>18.03470532701391</v>
+        <v>25.84941705281852</v>
       </c>
       <c r="D3" t="n">
-        <v>63.33745313948297</v>
+        <v>72.74750488468865</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.37304843208056</v>
+        <v>25.85727103445249</v>
       </c>
       <c r="C4" t="n">
-        <v>68.1912137892792</v>
+        <v>94.55899362994005</v>
       </c>
       <c r="D4" t="n">
-        <v>165.124073368088</v>
+        <v>176.7891995899486</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.92062697133881</v>
+        <v>46.19122948481243</v>
       </c>
       <c r="C5" t="n">
-        <v>194.2633269778377</v>
+        <v>211.5666302651877</v>
       </c>
       <c r="D5" t="n">
-        <v>186.8020444255619</v>
+        <v>176.9109363052752</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.41015922285948</v>
+        <v>48.18123208132072</v>
       </c>
       <c r="C6" t="n">
-        <v>353.4900418865151</v>
+        <v>338.5566775572169</v>
       </c>
       <c r="D6" t="n">
-        <v>115.3209940793516</v>
+        <v>96.885735689005</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>23.53543771390878</v>
       </c>
       <c r="C7" t="n">
-        <v>378.6630347711074</v>
+        <v>369.0212905676995</v>
       </c>
       <c r="D7" t="n">
-        <v>57.25159912085699</v>
+        <v>50.84373185523806</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>246.6739281690536</v>
+        <v>280.0533501134451</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>106.2781159755342</v>
+        <v>133.7906136393468</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>18.44213062427633</v>
+      </c>
+      <c r="D12" t="n">
         <v>19.96089432274615</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.680572143221292</v>
+        <v>4.427682146153115</v>
       </c>
       <c r="C2" t="n">
-        <v>2.546653544816226</v>
+        <v>10.42027013287565</v>
       </c>
       <c r="D2" t="n">
-        <v>15.19352747092364</v>
+        <v>8.79056894382594</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.334195130071415</v>
+        <v>1.976258128648829</v>
       </c>
       <c r="C2" t="n">
-        <v>5.981788761975816</v>
+        <v>9.201921231905354</v>
       </c>
       <c r="D2" t="n">
-        <v>9.627999735548469</v>
+        <v>15.0963344482032</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.370781837035805</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81643854150163</v>
+        <v>39.10791979867169</v>
       </c>
       <c r="D3" t="n">
-        <v>69.30157044278234</v>
+        <v>80.73893119725768</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>35.40378571054848</v>
       </c>
       <c r="C4" t="n">
-        <v>102.4846428463245</v>
+        <v>130.4349999862312</v>
       </c>
       <c r="D4" t="n">
-        <v>169.1443302169787</v>
+        <v>179.0992519380414</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.53173170727006</v>
+        <v>27.14532402242431</v>
       </c>
       <c r="C5" t="n">
-        <v>296.2914571416874</v>
+        <v>299.9239236474006</v>
       </c>
       <c r="D5" t="n">
-        <v>169.6214596012427</v>
+        <v>155.1897683488146</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.85286101755</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="C6" t="n">
-        <v>311.7490747450535</v>
+        <v>299.4723197034471</v>
       </c>
       <c r="D6" t="n">
-        <v>88.15112636432112</v>
+        <v>75.99512629033711</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.551382356888213</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>173.4316224414245</v>
+        <v>196.9071735453743</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>78.27474445959818</v>
+        <v>98.55274329081605</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>14.74879576089983</v>
+      </c>
+      <c r="D11" t="n">
         <v>15.99267010218054</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.135522240915065</v>
+        <v>5.88165049614264</v>
       </c>
       <c r="C2" t="n">
-        <v>4.869468613064179</v>
+        <v>6.721044783273664</v>
       </c>
       <c r="D2" t="n">
-        <v>20.23185668911827</v>
+        <v>15.02466686579319</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.829437941368314</v>
+        <v>9.410051745205678</v>
       </c>
       <c r="C3" t="n">
-        <v>6.415721247252906</v>
+        <v>26.25684235008094</v>
       </c>
       <c r="D3" t="n">
-        <v>15.89940407027709</v>
+        <v>10.51942665100457</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39832464281328</v>
+        <v>13.39794381849072</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14417018884599</v>
+        <v>70.14217646151023</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576273487389797</v>
+        <v>1.57622868452832</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.854341486872978</v>
+        <v>4.57985304031137</v>
       </c>
       <c r="C2" t="n">
-        <v>5.552765015219959</v>
+        <v>7.784277546972959</v>
       </c>
       <c r="D2" t="n">
-        <v>32.81099002363265</v>
+        <v>19.2972328746753</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.74446785945534</v>
+        <v>15.92394776288327</v>
       </c>
       <c r="C3" t="n">
-        <v>14.41205629834318</v>
+        <v>26.22738991895354</v>
       </c>
       <c r="D3" t="n">
-        <v>29.04991456866312</v>
+        <v>20.59706683509808</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9.265734832681398</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="C4" t="n">
-        <v>10.47819324742621</v>
+        <v>40.55992465325273</v>
       </c>
       <c r="D4" t="n">
-        <v>23.40682876465245</v>
+        <v>20.58626761035137</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44308806968222</v>
+        <v>15.44013555467535</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15617554664819</v>
+        <v>86.13970362082036</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251176435722573</v>
+        <v>3.250554853615862</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.17046424764045</v>
+        <v>3.929936060099982</v>
       </c>
       <c r="C2" t="n">
-        <v>8.310494316449249</v>
+        <v>9.973574927443346</v>
       </c>
       <c r="D2" t="n">
-        <v>27.65779632404114</v>
+        <v>18.44311237198058</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.52357462599981</v>
+        <v>15.89449533175586</v>
       </c>
       <c r="C3" t="n">
-        <v>18.77592484372025</v>
+        <v>28.69157665661304</v>
       </c>
       <c r="D3" t="n">
-        <v>48.55724145204724</v>
+        <v>31.25393816469721</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.01645303126072</v>
+        <v>22.27094667083889</v>
       </c>
       <c r="C4" t="n">
-        <v>25.53820303057228</v>
+        <v>55.36468003329463</v>
       </c>
       <c r="D4" t="n">
-        <v>32.69808903764427</v>
+        <v>26.27844079957437</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.811185645615124</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C5" t="n">
-        <v>13.30268139254428</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="D5" t="n">
-        <v>30.82687791334985</v>
+        <v>30.06602344255857</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73912655292934</v>
+        <v>16.73141139910734</v>
       </c>
       <c r="C21" t="n">
-        <v>102.108671972869</v>
+        <v>102.0616095345548</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021737965878803</v>
+        <v>4.182852849776835</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.642684893383167</v>
+        <v>4.774239085752239</v>
       </c>
       <c r="C2" t="n">
-        <v>10.9415781638307</v>
+        <v>8.742463306317847</v>
       </c>
       <c r="D2" t="n">
-        <v>21.9312619651695</v>
+        <v>23.47358760854123</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.94572613882594</v>
+        <v>14.53968349989526</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69862881699201</v>
+        <v>34.45934441906304</v>
       </c>
       <c r="D3" t="n">
-        <v>58.77723505325654</v>
+        <v>38.31761289675301</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.81974363751286</v>
+        <v>26.623034243765</v>
       </c>
       <c r="C4" t="n">
-        <v>37.73936349895164</v>
+        <v>64.54107582488956</v>
       </c>
       <c r="D4" t="n">
-        <v>48.4472857091716</v>
+        <v>35.50588747179015</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.87409961414493</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="C5" t="n">
-        <v>31.93134408062751</v>
+        <v>75.91364123088462</v>
       </c>
       <c r="D5" t="n">
-        <v>35.7356164345839</v>
+        <v>32.39767424014475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.976119259928589</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>16.9459471230042</v>
+        <v>42.7070068824405</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06999613186711</v>
+        <v>18.05313481171148</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8852128602759</v>
+        <v>117.7752128192606</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883808050235088</v>
+        <v>6.017711603903827</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.546874528994478</v>
+        <v>6.178138302825178</v>
       </c>
       <c r="C2" t="n">
-        <v>9.498409038587891</v>
+        <v>7.967864367667113</v>
       </c>
       <c r="D2" t="n">
-        <v>30.86712956922397</v>
+        <v>40.09653973684823</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.47939597930871</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C3" t="n">
-        <v>33.79666471869645</v>
+        <v>32.04915380513713</v>
       </c>
       <c r="D3" t="n">
-        <v>58.68396902135309</v>
+        <v>44.81187396034566</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.45489334443154</v>
+        <v>20.01194520336698</v>
       </c>
       <c r="C4" t="n">
-        <v>45.52462279362884</v>
+        <v>63.41795645123121</v>
       </c>
       <c r="D4" t="n">
-        <v>57.20251173564466</v>
+        <v>40.2280939292173</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.29701189049706</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C5" t="n">
-        <v>39.09810232162923</v>
+        <v>73.65562151111696</v>
       </c>
       <c r="D5" t="n">
-        <v>36.57010198319369</v>
+        <v>30.2132855981956</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.499390786292139</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>23.30570875111504</v>
+        <v>55.6680400739069</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>14.79199265988669</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065114695889962</v>
+        <v>7.053275242897548</v>
       </c>
       <c r="C21" t="n">
-        <v>66.2354502739684</v>
+        <v>66.12445540216451</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298836021917472</v>
+        <v>4.408297026810968</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.73064127613788</v>
+        <v>4.320671646390212</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34605821798039</v>
+        <v>8.38118015115502</v>
       </c>
       <c r="D2" t="n">
-        <v>27.97882782332985</v>
+        <v>40.03370788377644</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15604113171301</v>
+        <v>18.51085296357361</v>
       </c>
       <c r="C3" t="n">
-        <v>35.99577957620931</v>
+        <v>31.45028770554657</v>
       </c>
       <c r="D3" t="n">
-        <v>71.10307748007524</v>
+        <v>67.66205177669018</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.52169324604933</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="C4" t="n">
-        <v>70.5906051784584</v>
+        <v>73.94720057927826</v>
       </c>
       <c r="D4" t="n">
-        <v>75.60635419945537</v>
+        <v>54.38195058134357</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.9483525867692</v>
+        <v>25.20637230653686</v>
       </c>
       <c r="C5" t="n">
-        <v>67.1024555852695</v>
+        <v>99.23014920674639</v>
       </c>
       <c r="D5" t="n">
-        <v>50.24093876483053</v>
+        <v>38.04272353956391</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.90569546713008</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C6" t="n">
-        <v>46.49066253460771</v>
+        <v>91.8542787047401</v>
       </c>
       <c r="D6" t="n">
-        <v>36.30699359845555</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>26.05067533218911</v>
+        <v>58.03012505032471</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>19.61041039233004</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289351831715519</v>
+        <v>7.27123138890112</v>
       </c>
       <c r="C21" t="n">
-        <v>75.6270252540485</v>
+        <v>75.43902565984912</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378182852751078</v>
+        <v>5.45342354167584</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.603995822290041</v>
+        <v>3.517602024316322</v>
       </c>
       <c r="C2" t="n">
-        <v>10.47132101349648</v>
+        <v>6.274349577841365</v>
       </c>
       <c r="D2" t="n">
-        <v>36.18623863083318</v>
+        <v>35.27714025670064</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.76548547187203</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="C3" t="n">
-        <v>40.94378800561323</v>
+        <v>32.088423713307</v>
       </c>
       <c r="D3" t="n">
-        <v>76.98865496703488</v>
+        <v>83.03622082519523</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.03518835309942</v>
+        <v>30.93683365622549</v>
       </c>
       <c r="C4" t="n">
-        <v>82.14086691892213</v>
+        <v>75.97647308395641</v>
       </c>
       <c r="D4" t="n">
-        <v>94.27821378652546</v>
+        <v>74.36837034440013</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.94330497952772</v>
+        <v>31.24412068765475</v>
       </c>
       <c r="C5" t="n">
-        <v>102.6171787863979</v>
+        <v>120.2640937702343</v>
       </c>
       <c r="D5" t="n">
-        <v>65.58074664368695</v>
+        <v>49.01375413452202</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.55351008321273</v>
+        <v>27.25037102677872</v>
       </c>
       <c r="C6" t="n">
-        <v>80.10079518949728</v>
+        <v>127.5574974650838</v>
       </c>
       <c r="D6" t="n">
-        <v>44.19631814978292</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>48.80758711663017</v>
+        <v>98.03438050297373</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>53.82431788533138</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.4062479275757</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500329821643245</v>
+        <v>7.474156371998776</v>
       </c>
       <c r="C21" t="n">
-        <v>85.31625172119192</v>
+        <v>84.08425918498624</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500329821643245</v>
+        <v>6.53988682549893</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764321942</v>
+        <v>10.84497639101402</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907229028454</v>
+        <v>37.78907214679312</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.122759520759856</v>
+        <v>8.409650834578178</v>
       </c>
       <c r="C2" t="n">
-        <v>8.503898614185871</v>
+        <v>10.39081770174824</v>
       </c>
       <c r="D2" t="n">
-        <v>32.81982575297087</v>
+        <v>22.46925970709675</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05862712481433</v>
+        <v>23.64539345678443</v>
       </c>
       <c r="C3" t="n">
-        <v>28.08780181850124</v>
+        <v>22.72255061479242</v>
       </c>
       <c r="D3" t="n">
-        <v>90.76257525761763</v>
+        <v>65.06042036043613</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.35800342134737</v>
+        <v>44.68228326338508</v>
       </c>
       <c r="C4" t="n">
-        <v>77.38037230102935</v>
+        <v>67.56584050167397</v>
       </c>
       <c r="D4" t="n">
-        <v>96.56274069430778</v>
+        <v>91.99368687874312</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.31270415823178</v>
+        <v>49.67643383488862</v>
       </c>
       <c r="C5" t="n">
-        <v>130.4006388165826</v>
+        <v>130.7197068204628</v>
       </c>
       <c r="D5" t="n">
-        <v>62.39006660488482</v>
+        <v>65.21259125459439</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.49566908412018</v>
+        <v>46.85292743747478</v>
       </c>
       <c r="C6" t="n">
-        <v>157.7462393706733</v>
+        <v>157.0619612208132</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>44.80009298789471</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.3139636433765</v>
+        <v>35.57264631567892</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0928530635346</v>
+        <v>131.2714490302495</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C8" t="n">
-        <v>90.54168202416209</v>
+        <v>81.61268665403733</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>48.36874589283183</v>
+        <v>44.26405874137593</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>28.96450251839364</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.661517634975018</v>
+        <v>7.654968073641624</v>
       </c>
       <c r="C21" t="n">
-        <v>92.89590132407209</v>
+        <v>92.81648789290469</v>
       </c>
       <c r="D21" t="n">
-        <v>7.661517634975018</v>
+        <v>7.654968073641624</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.530585728649783</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C2" t="n">
-        <v>13.98205080388307</v>
+        <v>8.068002633500289</v>
       </c>
       <c r="D2" t="n">
-        <v>39.63119132503524</v>
+        <v>23.79854609864693</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37907778702628</v>
+        <v>25.54016652598077</v>
       </c>
       <c r="C3" t="n">
-        <v>30.34582153826891</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D3" t="n">
-        <v>94.19378348396022</v>
+        <v>66.84229244364408</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.75440850968483</v>
+        <v>44.17177445717674</v>
       </c>
       <c r="C4" t="n">
-        <v>73.75575977695013</v>
+        <v>62.24378619695202</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1114809077195</v>
+        <v>100.1618277780766</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.3378697456437</v>
+        <v>57.45678439104459</v>
       </c>
       <c r="C5" t="n">
-        <v>134.5485228670254</v>
+        <v>126.3754732291707</v>
       </c>
       <c r="D5" t="n">
-        <v>79.42338927356697</v>
+        <v>80.38059328520761</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>55.54728510628455</v>
       </c>
       <c r="C6" t="n">
-        <v>180.4884249395506</v>
+        <v>178.7978553928376</v>
       </c>
       <c r="D6" t="n">
-        <v>51.84413276586557</v>
+        <v>52.68941753922207</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.62013005838127</v>
+        <v>44.49575119957818</v>
       </c>
       <c r="C7" t="n">
-        <v>179.0609637775758</v>
+        <v>175.3479939601143</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.69247628885927</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="C8" t="n">
-        <v>133.2673421129833</v>
+        <v>122.419029981056</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>77.21249344360311</v>
+        <v>70.0015565559103</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>33.04071898642641</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.83244891734561</v>
+        <v>7.826338185435055</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8427798108247</v>
+        <v>100.7641041374763</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811505032013811</v>
+        <v>8.804630458614437</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.394122797759476</v>
+        <v>9.554368657729958</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98615772114931</v>
+        <v>9.308931731668256</v>
       </c>
       <c r="D2" t="n">
-        <v>35.42145716922492</v>
+        <v>21.8851198230699</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.78926840095221</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C3" t="n">
-        <v>40.65417243286042</v>
+        <v>31.32266050399448</v>
       </c>
       <c r="D3" t="n">
-        <v>100.6389571623405</v>
+        <v>68.82051406770141</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.18008610270045</v>
+        <v>44.82267318509238</v>
       </c>
       <c r="C4" t="n">
-        <v>73.62813257539804</v>
+        <v>68.24226466990004</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4650332544354</v>
+        <v>107.71735810996</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.28878236043136</v>
+        <v>60.35294011857268</v>
       </c>
       <c r="C5" t="n">
-        <v>134.6712413300562</v>
+        <v>119.8223073033232</v>
       </c>
       <c r="D5" t="n">
-        <v>95.05772146369743</v>
+        <v>92.23519681398784</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.10072876957248</v>
+        <v>63.95988118397546</v>
       </c>
       <c r="C6" t="n">
-        <v>192.6041733576605</v>
+        <v>186.687179944165</v>
       </c>
       <c r="D6" t="n">
-        <v>61.70578845502478</v>
+        <v>62.63157654012953</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.5669768136317</v>
+        <v>53.11942303368217</v>
       </c>
       <c r="C7" t="n">
-        <v>211.3997331554657</v>
+        <v>210.8008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>45.63359678880023</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="C8" t="n">
-        <v>175.1585166531947</v>
+        <v>166.5633155025138</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>18.52656092684155</v>
       </c>
       <c r="C9" t="n">
-        <v>113.3781153726471</v>
+        <v>102.8390537675576</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>61.78138302825178</v>
+        <v>57.65313393189394</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1556,7 +1556,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>29.65859814529614</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.986210175676614</v>
+        <v>7.981725040348115</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8138373716343</v>
+        <v>107.7532880446995</v>
       </c>
       <c r="D21" t="n">
-        <v>9.982762719595769</v>
+        <v>9.977156300435142</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.969026041820607</v>
+        <v>8.921141388490765</v>
       </c>
       <c r="C2" t="n">
-        <v>8.438121518001335</v>
+        <v>6.478553100324701</v>
       </c>
       <c r="D2" t="n">
-        <v>29.30320547635879</v>
+        <v>18.16822301479147</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14546289114455</v>
+        <v>31.81844309463912</v>
       </c>
       <c r="C3" t="n">
-        <v>57.01008918561228</v>
+        <v>45.99487994396307</v>
       </c>
       <c r="D3" t="n">
-        <v>107.0792221021996</v>
+        <v>75.49148971805849</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.31825048709199</v>
+        <v>28.99690019263379</v>
       </c>
       <c r="C4" t="n">
-        <v>106.0964926502486</v>
+        <v>96.49892709353173</v>
       </c>
       <c r="D4" t="n">
-        <v>118.6805347232842</v>
+        <v>103.4673722982756</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.09623663721197</v>
+        <v>36.03014074585795</v>
       </c>
       <c r="C5" t="n">
-        <v>115.0853746303324</v>
+        <v>111.5510828950438</v>
       </c>
       <c r="D5" t="n">
-        <v>62.41461029749098</v>
+        <v>62.21826075664162</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.94973524510094</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>139.2304776685784</v>
+        <v>138.8279611098372</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>30.22899356146354</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>123.186756685777</v>
+        <v>117.1382090799124</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.60772719112455</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C8" t="n">
-        <v>83.53200341583985</v>
+        <v>75.77128781376882</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>28.07602084605028</v>
@@ -1853,7 +1853,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
         <v>24.0832529328785</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526437753654543</v>
+        <v>5.39274013942773</v>
       </c>
       <c r="C2" t="n">
-        <v>3.865140711619692</v>
+        <v>4.023202092003429</v>
       </c>
       <c r="D2" t="n">
-        <v>20.2514916432032</v>
+        <v>12.96692367769187</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.97994843975434</v>
+        <v>32.07860623626453</v>
       </c>
       <c r="C3" t="n">
-        <v>46.08814597586652</v>
+        <v>36.35902622678062</v>
       </c>
       <c r="D3" t="n">
-        <v>106.1269268290802</v>
+        <v>73.95505456091222</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.60576369571606</v>
+        <v>42.02763747110171</v>
       </c>
       <c r="C4" t="n">
-        <v>125.5468781667864</v>
+        <v>107.6790699494944</v>
       </c>
       <c r="D4" t="n">
-        <v>140.3516335468283</v>
+        <v>114.6730405945487</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.67332436085985</v>
+        <v>40.6934423410303</v>
       </c>
       <c r="C5" t="n">
-        <v>153.2017292477148</v>
+        <v>144.4150872947058</v>
       </c>
       <c r="D5" t="n">
-        <v>80.79783605951251</v>
+        <v>79.17795234750527</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.33716573537994</v>
+        <v>38.76234460677682</v>
       </c>
       <c r="C6" t="n">
-        <v>162.5361864196935</v>
+        <v>162.1336698609523</v>
       </c>
       <c r="D6" t="n">
-        <v>36.79001346894498</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>155.3458662337898</v>
+        <v>148.9978855781299</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.00319158948677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>108.5665698741335</v>
+        <v>100.8893028269235</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>28.78680618392497</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.473423377625215</v>
+        <v>5.028511741152163</v>
       </c>
       <c r="C2" t="n">
-        <v>13.90252923983908</v>
+        <v>8.668832228499335</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76923253623977</v>
+        <v>13.13872952593506</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="C3" t="n">
-        <v>30.29182541453534</v>
+        <v>25.65797625049039</v>
       </c>
       <c r="D3" t="n">
-        <v>99.34795893125597</v>
+        <v>67.74059159302992</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.40003864618074</v>
+        <v>51.33166046424873</v>
       </c>
       <c r="C4" t="n">
-        <v>120.2375865822196</v>
+        <v>99.12804744550469</v>
       </c>
       <c r="D4" t="n">
-        <v>155.5520332516816</v>
+        <v>123.8494363861436</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>50.58455046131692</v>
       </c>
       <c r="C5" t="n">
-        <v>191.293540172491</v>
+        <v>170.2841393016093</v>
       </c>
       <c r="D5" t="n">
-        <v>107.3786551519949</v>
+        <v>98.4692947359551</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.32837106377072</v>
+        <v>45.92713935237005</v>
       </c>
       <c r="C6" t="n">
-        <v>198.4809151152819</v>
+        <v>195.14002767773</v>
       </c>
       <c r="D6" t="n">
-        <v>50.07305990740432</v>
+        <v>49.83154997215961</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.27781890476862</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="C7" t="n">
-        <v>192.3557911884861</v>
+        <v>189.2416874706151</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>150.7915386337888</v>
+        <v>143.6149629157447</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>84.53436782187582</v>
+        <v>79.65311823636068</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
         <v>29.852984190737</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.0930861054542</v>
+        <v>3.044399630869359</v>
       </c>
       <c r="C2" t="n">
-        <v>6.698464586075987</v>
+        <v>4.130212591766331</v>
       </c>
       <c r="D2" t="n">
-        <v>11.70439613003047</v>
+        <v>9.174432296186444</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12520604225386</v>
+        <v>24.29334694158732</v>
       </c>
       <c r="C3" t="n">
-        <v>42.01389300324225</v>
+        <v>30.7188856658827</v>
       </c>
       <c r="D3" t="n">
-        <v>95.50932540765095</v>
+        <v>66.00780689503431</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>56.0793923619863</v>
       </c>
       <c r="C4" t="n">
-        <v>117.6850425511779</v>
+        <v>96.30748629120362</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7314153441183</v>
+        <v>131.034847833526</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.9810533606456</v>
+        <v>51.66447293598841</v>
       </c>
       <c r="C5" t="n">
-        <v>229.778050178966</v>
+        <v>203.5162990903638</v>
       </c>
       <c r="D5" t="n">
-        <v>110.3484419573415</v>
+        <v>103.6971012610694</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.76735115628929</v>
+        <v>37.95731148929444</v>
       </c>
       <c r="C6" t="n">
-        <v>232.2923060495421</v>
+        <v>229.6759484177244</v>
       </c>
       <c r="D6" t="n">
-        <v>48.70450360768427</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>197.8054726947601</v>
+        <v>194.9309154167254</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>105.1451791248334</v>
+        <v>100.8893028269235</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
         <v>23.34596040698915</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.750857067299563</v>
+        <v>4.308890673939251</v>
       </c>
       <c r="C2" t="n">
-        <v>7.799985510240909</v>
+        <v>5.665666001208343</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30192062901829</v>
+        <v>14.08513431282899</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.91841712955628</v>
+        <v>17.49474408967816</v>
       </c>
       <c r="C3" t="n">
-        <v>34.23354244708628</v>
+        <v>23.42940896185013</v>
       </c>
       <c r="D3" t="n">
-        <v>84.50884238156544</v>
+        <v>59.4644584462293</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.74463209037137</v>
+        <v>52.03361007278519</v>
       </c>
       <c r="C4" t="n">
-        <v>112.5544290487841</v>
+        <v>86.722683454642</v>
       </c>
       <c r="D4" t="n">
-        <v>176.6360469480861</v>
+        <v>133.2810865808427</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.58959806855839</v>
+        <v>65.08987279156354</v>
       </c>
       <c r="C5" t="n">
-        <v>225.7283408989479</v>
+        <v>193.1343171179538</v>
       </c>
       <c r="D5" t="n">
-        <v>139.1627370769854</v>
+        <v>121.8839774822415</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.89818564286137</v>
+        <v>50.19381487502668</v>
       </c>
       <c r="C6" t="n">
-        <v>289.4496573907914</v>
+        <v>272.8257235147801</v>
       </c>
       <c r="D6" t="n">
-        <v>64.56365602208724</v>
+        <v>64.52340436621313</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>254.6977521558627</v>
+        <v>256.1949174048391</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>165.5619328441821</v>
+        <v>163.0584761983527</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.821141991377833</v>
+        <v>3.063052837250048</v>
       </c>
       <c r="C2" t="n">
-        <v>4.212679398923063</v>
+        <v>3.137665662772806</v>
       </c>
       <c r="D2" t="n">
-        <v>12.39947350463721</v>
+        <v>10.34467555964864</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.9415781638307</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>33.14871123389355</v>
+        <v>23.237968159522</v>
       </c>
       <c r="D3" t="n">
-        <v>79.70809610779854</v>
+        <v>58.11455535288994</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.38803668955152</v>
+        <v>45.81816535719864</v>
       </c>
       <c r="C4" t="n">
-        <v>103.5567113393621</v>
+        <v>76.4231682893887</v>
       </c>
       <c r="D4" t="n">
-        <v>178.3334887287288</v>
+        <v>133.1662220994459</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>71.66758241001718</v>
       </c>
       <c r="C5" t="n">
-        <v>226.5628264475577</v>
+        <v>187.1701998146544</v>
       </c>
       <c r="D5" t="n">
-        <v>158.7731474693154</v>
+        <v>133.5422314701724</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>59.37119241432587</v>
       </c>
       <c r="C6" t="n">
-        <v>324.3075913777787</v>
+        <v>297.4597369097411</v>
       </c>
       <c r="D6" t="n">
-        <v>77.60519252530189</v>
+        <v>77.32343093418305</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>309.9730931480709</v>
+        <v>308.8352475588488</v>
       </c>
       <c r="D7" t="n">
-        <v>42.75903951076558</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>207.6200044941154</v>
+        <v>208.2875929330033</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>74.54999366968578</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.677225989481052</v>
+        <v>4.519966430352315</v>
       </c>
       <c r="C2" t="n">
-        <v>15.33489914033518</v>
+        <v>12.82849725139307</v>
       </c>
       <c r="D2" t="n">
-        <v>20.29174329907732</v>
+        <v>13.49117695175967</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.717919613711677</v>
+        <v>13.51375714895735</v>
       </c>
       <c r="C3" t="n">
-        <v>25.84941705281852</v>
+        <v>18.2359636063845</v>
       </c>
       <c r="D3" t="n">
-        <v>72.74750488468865</v>
+        <v>53.62796834448202</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.85727103445249</v>
+        <v>38.88800831292041</v>
       </c>
       <c r="C4" t="n">
-        <v>94.55899362994005</v>
+        <v>68.21673922958962</v>
       </c>
       <c r="D4" t="n">
-        <v>176.7891995899486</v>
+        <v>131.6985092815969</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>71.12762117268143</v>
       </c>
       <c r="C5" t="n">
-        <v>211.5666302651877</v>
+        <v>167.4370709592935</v>
       </c>
       <c r="D5" t="n">
-        <v>176.9109363052752</v>
+        <v>145.9367962362884</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.18123208132072</v>
+        <v>72.05046401467342</v>
       </c>
       <c r="C6" t="n">
-        <v>338.5566775572169</v>
+        <v>298.5465316183423</v>
       </c>
       <c r="D6" t="n">
-        <v>96.885735689005</v>
+        <v>93.98761646606842</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.53543771390878</v>
+        <v>35.99185258539232</v>
       </c>
       <c r="C7" t="n">
-        <v>369.0212905676995</v>
+        <v>357.1637417958066</v>
       </c>
       <c r="D7" t="n">
-        <v>50.84373185523806</v>
+        <v>50.60418541540184</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>280.0533501134451</v>
+        <v>286.3954402828795</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>133.7906136393468</v>
+        <v>137.8953007908027</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>50.25075624187299</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.427682146153115</v>
+        <v>8.862236526235957</v>
       </c>
       <c r="C2" t="n">
-        <v>10.42027013287565</v>
+        <v>8.58440192593411</v>
       </c>
       <c r="D2" t="n">
-        <v>8.79056894382594</v>
+        <v>5.426119561372121</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.976258128648829</v>
+        <v>3.270201602846125</v>
       </c>
       <c r="C2" t="n">
-        <v>9.201921231905354</v>
+        <v>7.49171673110741</v>
       </c>
       <c r="D2" t="n">
-        <v>15.0963344482032</v>
+        <v>10.03837027592364</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.67298020349457</v>
+        <v>18.16233252856599</v>
       </c>
       <c r="C3" t="n">
-        <v>39.10791979867169</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="D3" t="n">
-        <v>80.73893119725768</v>
+        <v>58.65942532874692</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.40378571054848</v>
+        <v>54.02459441699773</v>
       </c>
       <c r="C4" t="n">
-        <v>130.4349999862312</v>
+        <v>97.62204646719009</v>
       </c>
       <c r="D4" t="n">
-        <v>179.0992519380414</v>
+        <v>135.7825797312636</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.14532402242431</v>
+        <v>41.89608327873264</v>
       </c>
       <c r="C5" t="n">
-        <v>299.9239236474006</v>
+        <v>252.1864415283995</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1897683488146</v>
+        <v>133.1495323884737</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.61135108230528</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>299.4723197034471</v>
+        <v>290.8182136905115</v>
       </c>
       <c r="D6" t="n">
-        <v>75.99512629033711</v>
+        <v>75.02908654935825</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>196.9071735453743</v>
+        <v>201.3986692923034</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>98.55274329081605</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.88165049614264</v>
+        <v>7.864780858721198</v>
       </c>
       <c r="C2" t="n">
-        <v>6.721044783273664</v>
+        <v>7.790168033198441</v>
       </c>
       <c r="D2" t="n">
-        <v>15.02466686579319</v>
+        <v>18.25363506506094</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.410051745205678</v>
+        <v>18.81519475189012</v>
       </c>
       <c r="C3" t="n">
-        <v>26.25684235008094</v>
+        <v>21.62790192455724</v>
       </c>
       <c r="D3" t="n">
-        <v>10.51942665100457</v>
+        <v>7.69199326277376</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,7 +4568,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39794381849072</v>
+        <v>13.39807527064597</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14217646151023</v>
+        <v>70.14286465220539</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57622868452832</v>
+        <v>1.576244149487761</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.57985304031137</v>
+        <v>5.097234080449439</v>
       </c>
       <c r="C2" t="n">
-        <v>7.784277546972959</v>
+        <v>6.89775937003809</v>
       </c>
       <c r="D2" t="n">
-        <v>19.2972328746753</v>
+        <v>15.93867397844697</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>23.89573912136737</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22738991895354</v>
+        <v>27.1011453757332</v>
       </c>
       <c r="D3" t="n">
-        <v>20.59706683509808</v>
+        <v>21.16648050356123</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.0652783745658</v>
+        <v>21.6838615436993</v>
       </c>
       <c r="C4" t="n">
-        <v>40.55992465325273</v>
+        <v>33.51490312757761</v>
       </c>
       <c r="D4" t="n">
-        <v>20.58626761035137</v>
+        <v>19.10579207234717</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44013555467535</v>
+        <v>15.43871875826895</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13970362082036</v>
+        <v>86.13179938823734</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250554853615862</v>
+        <v>3.250256580688201</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.929936060099982</v>
+        <v>4.851797154387737</v>
       </c>
       <c r="C2" t="n">
-        <v>9.973574927443346</v>
+        <v>10.05505998689583</v>
       </c>
       <c r="D2" t="n">
-        <v>18.44311237198058</v>
+        <v>31.91269087424682</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.89449533175586</v>
+        <v>20.37126486312131</v>
       </c>
       <c r="C3" t="n">
-        <v>28.69157665661304</v>
+        <v>26.92933952749001</v>
       </c>
       <c r="D3" t="n">
-        <v>31.25393816469721</v>
+        <v>29.00573592197201</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.27094667083889</v>
+        <v>35.72285371442869</v>
       </c>
       <c r="C4" t="n">
-        <v>55.36468003329463</v>
+        <v>53.06739040535709</v>
       </c>
       <c r="D4" t="n">
-        <v>26.27844079957437</v>
+        <v>25.41057582902019</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.03837027592364</v>
+        <v>18.21141991377834</v>
       </c>
       <c r="C5" t="n">
-        <v>44.98858854711009</v>
+        <v>37.62548076525901</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>30.91916219754903</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73141139910734</v>
+        <v>16.72845574654714</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0616095345548</v>
+        <v>102.0435800539375</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182852849776835</v>
+        <v>4.182113936636785</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.774239085752239</v>
+        <v>5.517422097867075</v>
       </c>
       <c r="C2" t="n">
-        <v>8.742463306317847</v>
+        <v>10.67257929286708</v>
       </c>
       <c r="D2" t="n">
-        <v>23.47358760854123</v>
+        <v>26.03300387351267</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.53968349989526</v>
+        <v>18.29486846863931</v>
       </c>
       <c r="C3" t="n">
-        <v>34.45934441906304</v>
+        <v>33.75248607200535</v>
       </c>
       <c r="D3" t="n">
-        <v>38.31761289675301</v>
+        <v>46.80482179996669</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.623034243765</v>
+        <v>37.79041437957247</v>
       </c>
       <c r="C4" t="n">
-        <v>64.54107582488956</v>
+        <v>60.90370058065513</v>
       </c>
       <c r="D4" t="n">
-        <v>35.50588747179015</v>
+        <v>33.75739481052658</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.69662426385451</v>
+        <v>35.34291735288518</v>
       </c>
       <c r="C5" t="n">
-        <v>75.91364123088462</v>
+        <v>69.23775684200632</v>
       </c>
       <c r="D5" t="n">
-        <v>32.39767424014475</v>
+        <v>31.68590715456581</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>15.05411929692059</v>
       </c>
       <c r="C6" t="n">
-        <v>42.7070068824405</v>
+        <v>36.79001346894498</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05313481171148</v>
+        <v>18.04492773601581</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7752128192606</v>
+        <v>117.7216714206746</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017711603903827</v>
+        <v>6.014975912005272</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.178138302825178</v>
+        <v>8.610909113948773</v>
       </c>
       <c r="C2" t="n">
-        <v>7.967864367667113</v>
+        <v>6.383323573012761</v>
       </c>
       <c r="D2" t="n">
-        <v>40.09653973684823</v>
+        <v>29.53882492537803</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.85246010692249</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="C3" t="n">
-        <v>32.04915380513713</v>
+        <v>35.72579895754143</v>
       </c>
       <c r="D3" t="n">
-        <v>44.81187396034566</v>
+        <v>52.85238765812704</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.01194520336698</v>
+        <v>26.24015263910875</v>
       </c>
       <c r="C4" t="n">
-        <v>63.41795645123121</v>
+        <v>61.72051467058848</v>
       </c>
       <c r="D4" t="n">
-        <v>40.2280939292173</v>
+        <v>42.57643443777567</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.75138115111408</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="C5" t="n">
-        <v>73.65562151111696</v>
+        <v>67.81422267084844</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>29.28062527916113</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>55.6680400739069</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70942804173872</v>
+        <v>23.59532432386784</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053275242897548</v>
+        <v>7.048052873180604</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12445540216451</v>
+        <v>66.07549568606815</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408297026810968</v>
+        <v>4.405033045737877</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.320671646390212</v>
+        <v>7.609526455617027</v>
       </c>
       <c r="C2" t="n">
-        <v>8.38118015115502</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="D2" t="n">
-        <v>40.03370788377644</v>
+        <v>21.68680678681204</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.51085296357361</v>
+        <v>24.65168485363741</v>
       </c>
       <c r="C3" t="n">
-        <v>31.45028770554657</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="D3" t="n">
-        <v>67.66205177669018</v>
+        <v>64.89352325071417</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.47889725768997</v>
+        <v>30.17107044691297</v>
       </c>
       <c r="C4" t="n">
-        <v>73.94720057927826</v>
+        <v>78.97571232043042</v>
       </c>
       <c r="D4" t="n">
-        <v>54.38195058134357</v>
+        <v>60.39319177444678</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.20637230653686</v>
+        <v>35.07293673421731</v>
       </c>
       <c r="C5" t="n">
-        <v>99.23014920674639</v>
+        <v>95.69585747145786</v>
       </c>
       <c r="D5" t="n">
-        <v>38.04272353956391</v>
+        <v>38.18998569520093</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.11953654020664</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>91.8542787047401</v>
+        <v>83.60268925054564</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>58.03012505032471</v>
+        <v>51.44259795482861</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>28.53940576245478</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27123138890112</v>
+        <v>7.264706555664329</v>
       </c>
       <c r="C21" t="n">
-        <v>75.43902565984912</v>
+        <v>75.37133051501742</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45342354167584</v>
+        <v>5.448529916748247</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.517602024316322</v>
+        <v>6.514877765381833</v>
       </c>
       <c r="C2" t="n">
-        <v>6.274349577841365</v>
+        <v>5.482079180514189</v>
       </c>
       <c r="D2" t="n">
-        <v>35.27714025670064</v>
+        <v>17.1746943380937</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.49336143134641</v>
+        <v>25.53034904893831</v>
       </c>
       <c r="C3" t="n">
-        <v>32.088423713307</v>
+        <v>24.61241494546753</v>
       </c>
       <c r="D3" t="n">
-        <v>83.03622082519523</v>
+        <v>66.94046721406876</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.93683365622549</v>
+        <v>40.08770400751001</v>
       </c>
       <c r="C4" t="n">
-        <v>75.97647308395641</v>
+        <v>74.41942122502097</v>
       </c>
       <c r="D4" t="n">
-        <v>74.36837034440013</v>
+        <v>77.72496574521998</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.24412068765475</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="C5" t="n">
-        <v>120.2640937702343</v>
+        <v>123.8965602759475</v>
       </c>
       <c r="D5" t="n">
-        <v>49.01375413452202</v>
+        <v>51.24723016168351</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.25037102677872</v>
+        <v>39.08435785376978</v>
       </c>
       <c r="C6" t="n">
-        <v>127.5574974650838</v>
+        <v>120.6744643106095</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="C7" t="n">
-        <v>98.03438050297373</v>
+        <v>88.57229612944299</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>53.82431788533138</v>
+        <v>48.23326470964579</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474156371998776</v>
+        <v>7.467301715170616</v>
       </c>
       <c r="C21" t="n">
-        <v>84.08425918498624</v>
+        <v>84.00714429566943</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53988682549893</v>
+        <v>6.533889000774289</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_96_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639101402</v>
+        <v>10.84497632276848</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907214679312</v>
+        <v>37.78907190899312</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.409650834578178</v>
+        <v>1.074031988446011</v>
       </c>
       <c r="C2" t="n">
-        <v>10.39081770174824</v>
+        <v>2.604576659366788</v>
       </c>
       <c r="D2" t="n">
-        <v>22.46925970709675</v>
+        <v>14.62607729786898</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.64539345678443</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C3" t="n">
-        <v>22.72255061479242</v>
+        <v>29.20208546282137</v>
       </c>
       <c r="D3" t="n">
-        <v>65.06042036043613</v>
+        <v>75.04970325114742</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.68228326338508</v>
+        <v>18.49318150489717</v>
       </c>
       <c r="C4" t="n">
-        <v>67.56584050167397</v>
+        <v>101.3232353122006</v>
       </c>
       <c r="D4" t="n">
-        <v>91.99368687874312</v>
+        <v>96.19262180980672</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.67643383488862</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7197068204628</v>
+        <v>113.3427724552943</v>
       </c>
       <c r="D5" t="n">
-        <v>65.21259125459439</v>
+        <v>56.89227946110267</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.85292743747478</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>157.0619612208132</v>
+        <v>65.20768251607315</v>
       </c>
       <c r="D6" t="n">
-        <v>44.80009298789471</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.57264631567892</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>131.2714490302495</v>
+        <v>32.03933632809466</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.44213062427633</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>81.61268665403733</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.654968073641624</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.81648789290469</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.654968073641624</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.462084373530759</v>
+        <v>1.050470043544087</v>
       </c>
       <c r="C2" t="n">
-        <v>8.068002633500289</v>
+        <v>5.519385593275567</v>
       </c>
       <c r="D2" t="n">
-        <v>23.79854609864693</v>
+        <v>13.97321507454485</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.54016652598077</v>
+        <v>6.278276568658352</v>
       </c>
       <c r="C3" t="n">
-        <v>31.29320807286708</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="D3" t="n">
-        <v>66.84229244364408</v>
+        <v>69.47337629102553</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.17177445717674</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="C4" t="n">
-        <v>62.24378619695202</v>
+        <v>86.2887509693649</v>
       </c>
       <c r="D4" t="n">
-        <v>100.1618277780766</v>
+        <v>111.3036824735736</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.45678439104459</v>
+        <v>24.51914891356409</v>
       </c>
       <c r="C5" t="n">
-        <v>126.3754732291707</v>
+        <v>153.226272940321</v>
       </c>
       <c r="D5" t="n">
-        <v>80.38059328520761</v>
+        <v>77.28808801683016</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.54728510628455</v>
+        <v>20.85035774279376</v>
       </c>
       <c r="C6" t="n">
-        <v>178.7978553928376</v>
+        <v>125.3436563920073</v>
       </c>
       <c r="D6" t="n">
-        <v>52.68941753922207</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.49575119957818</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>175.3479939601143</v>
+        <v>63.53969316655781</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.20422888467911</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>122.419029981056</v>
+        <v>35.549084370777</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>70.0015565559103</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.826338185435055</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7641041374763</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.804630458614437</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.554368657729958</v>
+        <v>0.559596191420682</v>
       </c>
       <c r="C2" t="n">
-        <v>9.308931731668256</v>
+        <v>2.309070600388498</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8851198230699</v>
+        <v>9.419869222248145</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.5478405811655</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C3" t="n">
-        <v>31.32266050399448</v>
+        <v>21.00449213236051</v>
       </c>
       <c r="D3" t="n">
-        <v>68.82051406770141</v>
+        <v>67.63259934556277</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.82267318509238</v>
+        <v>20.08852152429823</v>
       </c>
       <c r="C4" t="n">
-        <v>68.24226466990004</v>
+        <v>78.04403374910019</v>
       </c>
       <c r="D4" t="n">
-        <v>107.71735810996</v>
+        <v>122.3051472473634</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.35294011857268</v>
+        <v>25.23091599914303</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8223073033232</v>
+        <v>175.5119458267235</v>
       </c>
       <c r="D5" t="n">
-        <v>92.23519681398784</v>
+        <v>86.6637785923872</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.95988118397546</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C6" t="n">
-        <v>186.687179944165</v>
+        <v>160.6443585936099</v>
       </c>
       <c r="D6" t="n">
-        <v>62.63157654012953</v>
+        <v>41.21769561509809</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.11942303368217</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>210.8008670558751</v>
+        <v>61.44366181799087</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.88287859022092</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>166.5633155025138</v>
+        <v>37.30150402285756</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.52656092684155</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>102.8390537675576</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>57.65313393189394</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.84931924182727</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.981725040348115</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7532880446995</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.977156300435142</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.921141388490765</v>
+        <v>1.059305772882308</v>
       </c>
       <c r="C2" t="n">
-        <v>6.478553100324701</v>
+        <v>7.275732236173111</v>
       </c>
       <c r="D2" t="n">
-        <v>18.16822301479147</v>
+        <v>10.926851948267</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.81844309463912</v>
+        <v>3.774819922828986</v>
       </c>
       <c r="C3" t="n">
-        <v>45.99487994396307</v>
+        <v>14.24515918862122</v>
       </c>
       <c r="D3" t="n">
-        <v>75.49148971805849</v>
+        <v>60.39711876526377</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.99690019263379</v>
+        <v>15.87682387307942</v>
       </c>
       <c r="C4" t="n">
-        <v>96.49892709353173</v>
+        <v>64.79633022799374</v>
       </c>
       <c r="D4" t="n">
-        <v>103.4673722982756</v>
+        <v>127.8314050745687</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.03014074585795</v>
+        <v>28.07798434145878</v>
       </c>
       <c r="C5" t="n">
-        <v>111.5510828950438</v>
+        <v>160.8348176482337</v>
       </c>
       <c r="D5" t="n">
-        <v>62.21826075664162</v>
+        <v>108.262228085817</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C6" t="n">
-        <v>138.8279611098372</v>
+        <v>221.9476304898934</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22899356146354</v>
+        <v>56.55357650313753</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1382090799124</v>
+        <v>140.9131932336574</v>
       </c>
       <c r="D7" t="n">
-        <v>27.60772719112455</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>75.77128781376882</v>
+        <v>57.41260574435346</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.91689560250429</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.39274013942773</v>
+        <v>0.5969026041820606</v>
       </c>
       <c r="C2" t="n">
-        <v>4.023202092003429</v>
+        <v>4.005530633326987</v>
       </c>
       <c r="D2" t="n">
-        <v>12.96692367769187</v>
+        <v>7.872634840355172</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.07860623626453</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="C3" t="n">
-        <v>36.35902622678062</v>
+        <v>21.95187866695868</v>
       </c>
       <c r="D3" t="n">
-        <v>73.95505456091222</v>
+        <v>56.13142499031139</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.02763747110171</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6790699494944</v>
+        <v>51.8932201510779</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6730405945487</v>
+        <v>129.6564740567635</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.6934423410303</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="C5" t="n">
-        <v>144.4150872947058</v>
+        <v>149.8883307458818</v>
       </c>
       <c r="D5" t="n">
-        <v>79.17795234750527</v>
+        <v>125.5164439879547</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.76234460677682</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>162.1336698609523</v>
+        <v>245.9376173908685</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>70.27939115621218</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>11.07902284242525</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9978855781299</v>
+        <v>206.1297114790688</v>
       </c>
       <c r="D7" t="n">
-        <v>30.00319158948677</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8893028269235</v>
+        <v>91.54306468249383</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>48.03593342109217</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.028511741152163</v>
+        <v>0.7107853378746907</v>
       </c>
       <c r="C2" t="n">
-        <v>8.668832228499335</v>
+        <v>11.35587569502286</v>
       </c>
       <c r="D2" t="n">
-        <v>13.13872952593506</v>
+        <v>8.910342163744051</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.18182861393069</v>
+        <v>2.901064466049325</v>
       </c>
       <c r="C3" t="n">
-        <v>25.65797625049039</v>
+        <v>18.70720250442297</v>
       </c>
       <c r="D3" t="n">
-        <v>67.74059159302992</v>
+        <v>50.07404165510857</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.33166046424873</v>
+        <v>10.08254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>99.12804744550469</v>
+        <v>53.29711936815084</v>
       </c>
       <c r="D4" t="n">
-        <v>123.8494363861436</v>
+        <v>128.3674393210875</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.58455046131692</v>
+        <v>24.88730430265665</v>
       </c>
       <c r="C5" t="n">
-        <v>170.2841393016093</v>
+        <v>123.675667042492</v>
       </c>
       <c r="D5" t="n">
-        <v>98.4692947359551</v>
+        <v>140.7089897111741</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.92713935237005</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>195.14002767773</v>
+        <v>245.8973657349944</v>
       </c>
       <c r="D6" t="n">
-        <v>49.83154997215961</v>
+        <v>88.83540451418115</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>189.2416874706151</v>
+        <v>273.322487853129</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>49.1669067763845</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>143.6149629157447</v>
+        <v>170.9860889101457</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>79.65311823636068</v>
+        <v>74.32811868852599</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42131830050468</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.044399630869359</v>
+        <v>0.4771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>4.130212591766331</v>
+        <v>5.904230693340318</v>
       </c>
       <c r="D2" t="n">
-        <v>9.174432296186444</v>
+        <v>6.414739499548659</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.29334694158732</v>
+        <v>4.015348110369454</v>
       </c>
       <c r="C3" t="n">
-        <v>30.7188856658827</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="D3" t="n">
-        <v>66.00780689503431</v>
+        <v>54.0010324720958</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.0793923619863</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>96.30748629120362</v>
+        <v>75.77226956147307</v>
       </c>
       <c r="D4" t="n">
-        <v>131.034847833526</v>
+        <v>133.2172729800667</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.66447293598841</v>
+        <v>20.61670178918302</v>
       </c>
       <c r="C5" t="n">
-        <v>203.5162990903638</v>
+        <v>196.8649583940917</v>
       </c>
       <c r="D5" t="n">
-        <v>103.6971012610694</v>
+        <v>129.4925221901543</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.95731148929444</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>229.6759484177244</v>
+        <v>240.2621339126177</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>72.77499382040757</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>194.9309154167254</v>
+        <v>120.2523127977833</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>100.8893028269235</v>
+        <v>54.74225198880214</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.308890673939251</v>
+        <v>0.2513274122871835</v>
       </c>
       <c r="C2" t="n">
-        <v>5.665666001208343</v>
+        <v>2.666426764734337</v>
       </c>
       <c r="D2" t="n">
-        <v>14.08513431282899</v>
+        <v>5.436918786118836</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.49474408967816</v>
+        <v>2.807798434145878</v>
       </c>
       <c r="C3" t="n">
-        <v>23.42940896185013</v>
+        <v>26.57100161543993</v>
       </c>
       <c r="D3" t="n">
-        <v>59.4644584462293</v>
+        <v>46.97171890968864</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.03361007278519</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="C4" t="n">
-        <v>86.722683454642</v>
+        <v>74.0110141800543</v>
       </c>
       <c r="D4" t="n">
-        <v>133.2810865808427</v>
+        <v>125.1384711218197</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.08987279156354</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C5" t="n">
-        <v>193.1343171179538</v>
+        <v>151.7781950765569</v>
       </c>
       <c r="D5" t="n">
-        <v>121.8839774822415</v>
+        <v>132.9531828476243</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.19381487502668</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>272.8257235147801</v>
+        <v>229.1526768913608</v>
       </c>
       <c r="D6" t="n">
-        <v>64.52340436621313</v>
+        <v>77.60519252530189</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>256.1949174048391</v>
+        <v>159.3582691010465</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>163.0584761983527</v>
+        <v>64.08849013323177</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>65.23124446097505</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.063052837250048</v>
+        <v>0.4859651136021712</v>
       </c>
       <c r="C2" t="n">
-        <v>3.137665662772806</v>
+        <v>4.292200962967055</v>
       </c>
       <c r="D2" t="n">
-        <v>10.34467555964864</v>
+        <v>9.738937226128359</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>1.73278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>23.237968159522</v>
+        <v>17.00387023755476</v>
       </c>
       <c r="D3" t="n">
-        <v>58.11455535288994</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.81816535719864</v>
+        <v>8.372344421816798</v>
       </c>
       <c r="C4" t="n">
-        <v>76.4231682893887</v>
+        <v>69.72274020790422</v>
       </c>
       <c r="D4" t="n">
-        <v>133.1662220994459</v>
+        <v>120.7480953884279</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.66758241001718</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="C5" t="n">
-        <v>187.1701998146544</v>
+        <v>144.9795922246477</v>
       </c>
       <c r="D5" t="n">
-        <v>133.5422314701724</v>
+        <v>148.5384276525424</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.37119241432587</v>
+        <v>18.71701998146544</v>
       </c>
       <c r="C6" t="n">
-        <v>297.4597369097411</v>
+        <v>236.6797365398211</v>
       </c>
       <c r="D6" t="n">
-        <v>77.32343093418305</v>
+        <v>100.7901463087946</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>308.8352475588488</v>
+        <v>251.5836484379919</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>208.2875929330033</v>
+        <v>138.9418438435298</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>54.1374954029861</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.519966430352315</v>
+        <v>0.559596191420682</v>
       </c>
       <c r="C2" t="n">
-        <v>12.82849725139307</v>
+        <v>7.077419199915256</v>
       </c>
       <c r="D2" t="n">
-        <v>13.49117695175967</v>
+        <v>16.56895600457342</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.51375714895735</v>
+        <v>1.678788574262046</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2359636063845</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="D3" t="n">
-        <v>53.62796834448202</v>
+        <v>38.83303044148258</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.88800831292041</v>
+        <v>5.819800390775091</v>
       </c>
       <c r="C4" t="n">
-        <v>68.21673922958962</v>
+        <v>55.28810371236337</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6985092815969</v>
+        <v>114.3667353108237</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.12762117268143</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="C5" t="n">
-        <v>167.4370709592935</v>
+        <v>135.2357462599982</v>
       </c>
       <c r="D5" t="n">
-        <v>145.9367962362884</v>
+        <v>156.2451471308799</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.05046401467342</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>298.5465316183423</v>
+        <v>234.7074054019893</v>
       </c>
       <c r="D6" t="n">
-        <v>93.98761646606842</v>
+        <v>122.6870471043154</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.99185258539232</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>357.1637417958066</v>
+        <v>298.7742970857275</v>
       </c>
       <c r="D7" t="n">
-        <v>50.60418541540184</v>
+        <v>64.37810570598458</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>286.3954402828795</v>
+        <v>234.2400934947677</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>137.8953007908027</v>
+        <v>110.3828031269901</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.862236526235957</v>
+        <v>5.929756133650734</v>
       </c>
       <c r="C2" t="n">
-        <v>8.58440192593411</v>
+        <v>3.584360868205105</v>
       </c>
       <c r="D2" t="n">
-        <v>5.426119561372121</v>
+        <v>17.81381209355838</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.270201602846125</v>
+        <v>0.6940956269024949</v>
       </c>
       <c r="C2" t="n">
-        <v>7.49171673110741</v>
+        <v>7.254133786679681</v>
       </c>
       <c r="D2" t="n">
-        <v>10.03837027592364</v>
+        <v>26.73004474352791</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.16233252856599</v>
+        <v>1.752419652080556</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6095107600838</v>
+        <v>21.95678740547991</v>
       </c>
       <c r="D3" t="n">
-        <v>58.65942532874692</v>
+        <v>41.91571823281757</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.02459441699773</v>
+        <v>4.505240214788612</v>
       </c>
       <c r="C4" t="n">
-        <v>97.62204646719009</v>
+        <v>48.21755674637784</v>
       </c>
       <c r="D4" t="n">
-        <v>135.7825797312636</v>
+        <v>107.7301208301152</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.89608327873264</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="C5" t="n">
-        <v>252.1864415283995</v>
+        <v>119.355977143806</v>
       </c>
       <c r="D5" t="n">
-        <v>133.1495323884737</v>
+        <v>161.2766041151448</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.33966901013618</v>
+        <v>21.77614582789851</v>
       </c>
       <c r="C6" t="n">
-        <v>290.8182136905115</v>
+        <v>226.8985841624101</v>
       </c>
       <c r="D6" t="n">
-        <v>75.02908654935825</v>
+        <v>139.0694710450819</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>201.3986692923034</v>
+        <v>316.9199399033213</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>81.08646988456105</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>309.0099986502047</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>41.97462309507237</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>188.0390465329127</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>81.28380117311467</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.864780858721198</v>
+        <v>5.739297079026853</v>
       </c>
       <c r="C2" t="n">
-        <v>7.790168033198441</v>
+        <v>12.86384016874596</v>
       </c>
       <c r="D2" t="n">
-        <v>18.25363506506094</v>
+        <v>27.90912373632833</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.81519475189012</v>
+        <v>9.788024611340701</v>
       </c>
       <c r="C3" t="n">
-        <v>21.62790192455724</v>
+        <v>7.073492209098269</v>
       </c>
       <c r="D3" t="n">
-        <v>7.69199326277376</v>
+        <v>15.12873212244335</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39807527064597</v>
+        <v>11.67761252060132</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14286465220539</v>
+        <v>59.94507760575345</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576244149487761</v>
+        <v>0.7785075013734214</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.097234080449439</v>
+        <v>3.221114217633785</v>
       </c>
       <c r="C2" t="n">
-        <v>6.89775937003809</v>
+        <v>4.648575379608647</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93867397844697</v>
+        <v>28.09761929554372</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.89573912136737</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C3" t="n">
-        <v>27.1011453757332</v>
+        <v>35.88778732874216</v>
       </c>
       <c r="D3" t="n">
-        <v>21.16648050356123</v>
+        <v>35.88778732874216</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.6838615436993</v>
+        <v>12.07353326682727</v>
       </c>
       <c r="C4" t="n">
-        <v>33.51490312757761</v>
+        <v>11.92038062496477</v>
       </c>
       <c r="D4" t="n">
-        <v>19.10579207234717</v>
+        <v>22.29647211114931</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43871875826895</v>
+        <v>13.62644232080008</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13179938823734</v>
+        <v>73.74309961844747</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250256580688201</v>
+        <v>1.603110861270597</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.851797154387737</v>
+        <v>2.128429022807085</v>
       </c>
       <c r="C2" t="n">
-        <v>10.05505998689583</v>
+        <v>4.695699269412493</v>
       </c>
       <c r="D2" t="n">
-        <v>31.91269087424682</v>
+        <v>27.92581344730052</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.37126486312131</v>
+        <v>13.33213382367169</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92933952749001</v>
+        <v>24.61732368398877</v>
       </c>
       <c r="D3" t="n">
-        <v>29.00573592197201</v>
+        <v>50.81526117181491</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>23.82799852977434</v>
       </c>
       <c r="C4" t="n">
-        <v>53.06739040535709</v>
+        <v>60.1124119310322</v>
       </c>
       <c r="D4" t="n">
-        <v>25.41057582902019</v>
+        <v>35.92705723691203</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.21141991377834</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C5" t="n">
-        <v>37.62548076525901</v>
+        <v>15.24163310843173</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>27.9798095710341</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72845574654714</v>
+        <v>14.83339908752225</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0435800539375</v>
+        <v>87.35223907096437</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182113936636785</v>
+        <v>2.472233181253709</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.517422097867075</v>
+        <v>1.795616551067416</v>
       </c>
       <c r="C2" t="n">
-        <v>10.67257929286708</v>
+        <v>8.834747590517047</v>
       </c>
       <c r="D2" t="n">
-        <v>26.03300387351267</v>
+        <v>23.90752009381833</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.29486846863931</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C3" t="n">
-        <v>33.75248607200535</v>
+        <v>20.76887268334127</v>
       </c>
       <c r="D3" t="n">
-        <v>46.80482179996669</v>
+        <v>61.36414025394689</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.79041437957247</v>
+        <v>25.21913502669207</v>
       </c>
       <c r="C4" t="n">
-        <v>60.90370058065513</v>
+        <v>61.05685322251763</v>
       </c>
       <c r="D4" t="n">
-        <v>33.75739481052658</v>
+        <v>53.29711936815084</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.34291735288518</v>
+        <v>23.8564692131975</v>
       </c>
       <c r="C5" t="n">
-        <v>69.23775684200632</v>
+        <v>69.8268054645544</v>
       </c>
       <c r="D5" t="n">
-        <v>31.68590715456581</v>
+        <v>34.3366259560322</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.05411929692059</v>
+        <v>10.02266231265569</v>
       </c>
       <c r="C6" t="n">
-        <v>36.79001346894498</v>
+        <v>18.03274183160542</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04492773601581</v>
+        <v>16.07092147205859</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7216714206746</v>
+        <v>100.6547186934196</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014975912005272</v>
+        <v>3.38335188885444</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.610909113948773</v>
+        <v>1.844703936279757</v>
       </c>
       <c r="C2" t="n">
-        <v>6.383323573012761</v>
+        <v>7.711628216858696</v>
       </c>
       <c r="D2" t="n">
-        <v>29.53882492537803</v>
+        <v>18.09851892778995</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.49336143134641</v>
+        <v>7.888342803623122</v>
       </c>
       <c r="C3" t="n">
-        <v>35.72579895754143</v>
+        <v>28.55904071653972</v>
       </c>
       <c r="D3" t="n">
-        <v>52.85238765812704</v>
+        <v>65.88508843200344</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.24015263910875</v>
+        <v>21.96464138711389</v>
       </c>
       <c r="C4" t="n">
-        <v>61.72051467058848</v>
+        <v>55.99005332089984</v>
       </c>
       <c r="D4" t="n">
-        <v>42.57643443777567</v>
+        <v>71.05006310404592</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27433388230815</v>
+        <v>31.14594591723007</v>
       </c>
       <c r="C5" t="n">
-        <v>67.81422267084844</v>
+        <v>93.04513866999146</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>44.71860792844222</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.86544381125596</v>
+        <v>20.89060939866788</v>
       </c>
       <c r="C6" t="n">
-        <v>50.31456984264904</v>
+        <v>65.97246397768143</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>23.59532432386784</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048052873180604</v>
+        <v>17.33346514321855</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07549568606815</v>
+        <v>114.4008699452425</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405033045737877</v>
+        <v>4.333366285804638</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.609526455617027</v>
+        <v>2.204023596034089</v>
       </c>
       <c r="C2" t="n">
-        <v>5.569454726192155</v>
+        <v>7.167739988705962</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68680678681204</v>
+        <v>27.52427863626357</v>
       </c>
     </row>
     <row r="3">
@@ -6081,10 +6081,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.65168485363741</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C3" t="n">
-        <v>28.86338250485623</v>
+        <v>29.19717672430014</v>
       </c>
       <c r="D3" t="n">
         <v>64.89352325071417</v>
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.17107044691297</v>
+        <v>18.5314696653628</v>
       </c>
       <c r="C4" t="n">
-        <v>78.97571232043042</v>
+        <v>63.3924310109208</v>
       </c>
       <c r="D4" t="n">
-        <v>60.39319177444678</v>
+        <v>86.21217464843366</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.07293673421731</v>
+        <v>32.07860623626453</v>
       </c>
       <c r="C5" t="n">
-        <v>95.69585747145786</v>
+        <v>98.24840150249958</v>
       </c>
       <c r="D5" t="n">
-        <v>38.18998569520093</v>
+        <v>57.92311455056183</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>31.11452999069417</v>
       </c>
       <c r="C6" t="n">
-        <v>83.60268925054564</v>
+        <v>106.0228615724301</v>
       </c>
       <c r="D6" t="n">
-        <v>33.61013265488955</v>
+        <v>42.74725853831463</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>51.44259795482861</v>
+        <v>56.89227946110266</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>26.28629478120835</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264706555664329</v>
+        <v>17.72939430952667</v>
       </c>
       <c r="C21" t="n">
-        <v>75.37133051501742</v>
+        <v>127.651639028592</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448529916748247</v>
+        <v>5.318818292858</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.514877765381833</v>
+        <v>1.990002596508285</v>
       </c>
       <c r="C2" t="n">
-        <v>5.482079180514189</v>
+        <v>4.471860792844222</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1746943380937</v>
+        <v>21.60728522276805</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.53034904893831</v>
+        <v>10.90721699418206</v>
       </c>
       <c r="C3" t="n">
-        <v>24.61241494546753</v>
+        <v>42.52440180945059</v>
       </c>
       <c r="D3" t="n">
-        <v>66.94046721406876</v>
+        <v>73.58199043329844</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.08770400751001</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="C4" t="n">
-        <v>74.41942122502097</v>
+        <v>88.59880331745765</v>
       </c>
       <c r="D4" t="n">
-        <v>77.72496574521998</v>
+        <v>78.70769519717103</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.54618018539328</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C5" t="n">
-        <v>123.8965602759475</v>
+        <v>63.34727061652545</v>
       </c>
       <c r="D5" t="n">
-        <v>51.24723016168351</v>
+        <v>42.77965621255477</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>120.6744643106095</v>
+        <v>37.47429161880501</v>
       </c>
       <c r="D6" t="n">
-        <v>37.79630486579796</v>
+        <v>26.12332466230338</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>88.57229612944299</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>26.76931465169778</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>48.23326470964579</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.467301715170616</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.00714429566943</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.533889000774289</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
